--- a/data/trans_camb/IP16A07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Clase-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,58</t>
+          <t>0,0; 16,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,95</t>
+          <t>0,0; 8,16</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,89</t>
+          <t>0,0; 11,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,31</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,14</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,82</t>
+          <t>0,29; 3,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,72</t>
+          <t>0,16; 1,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Clase-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,89</t>
+          <t>0,0; 19,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,16</t>
+          <t>0,0; 9,48</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,55</t>
+          <t>0,0; 11,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,48</t>
+          <t>0,0; 12,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,51</t>
+          <t>0,3; 3,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,67</t>
+          <t>0,17; 1,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir</t>
+          <t>Menores que consumieron pastillas para dormir</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,63</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,48</t>
+          <t>0,0; 9,68</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1488,24 +1488,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,29</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,08</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,52</t>
+          <t>0,0; 7,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1920,24 +1920,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,47</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,39; 4,14</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,78</t>
+          <t>0,18; 1,95</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
